--- a/Result/profitability/4994.xlsx
+++ b/Result/profitability/4994.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM68"/>
+  <dimension ref="A1:AM69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.18</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7287499999999999</v>
+        <v>0.6112499999999998</v>
       </c>
       <c r="N2" t="n">
-        <v>67.75999999999999</v>
+        <v>68.14375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2287499999999999</v>
+        <v>0.1274999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>68.56874999999999</v>
+        <v>68.89125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.07</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3537499999999999</v>
+        <v>0.2837499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>71.0925</v>
+        <v>71.25125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>2.09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5125</v>
+        <v>0.4949999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>73.96375</v>
+        <v>74.035</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.63</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6662499999999998</v>
+        <v>0.6375</v>
       </c>
       <c r="N6" t="n">
-        <v>75.98750000000001</v>
+        <v>76.12375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.53</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6712499999999998</v>
+        <v>0.6724999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>77.81</v>
+        <v>78.16499999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -9064,6 +9064,133 @@
       </c>
       <c r="AM68" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4994</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>292</v>
+      </c>
+      <c r="D69" t="n">
+        <v>93</v>
+      </c>
+      <c r="E69" t="n">
+        <v>199</v>
+      </c>
+      <c r="F69" t="n">
+        <v>68.14</v>
+      </c>
+      <c r="G69" t="n">
+        <v>27</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>9.13%</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J69" t="n">
+        <v>20</v>
+      </c>
+      <c r="K69" t="n">
+        <v>17</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.6137499999999999</v>
+      </c>
+      <c r="N69" t="n">
+        <v>66.57249999999999</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="X69" t="n">
+        <v>-0.3809523809523809</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1.120000000000005</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.01671142942405268</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0.5700000000000074</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0.008435696314932795</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
